--- a/data/configuración.xlsx
+++ b/data/configuración.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,6 +855,40 @@
       <c r="C25" s="1" t="inlineStr">
         <is>
           <t>Número de pagas extras anuales del cargo académico ocultas en el CR 68 (paga adicional del complemento específico) que hay que estimar para no contabilizarlas dos veces.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>másteres_ficticios_pod</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>49900</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Códigos de máster ficticios que deben descartarse al cargar el POD: no tienen alumnado matriculado y todas sus asignaturas pertenecen también a algún máster real, por el que se captura su coste y dedicación. Lista separada por comas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>umbral_residual_regla23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Umbral por persona (€) para la regla escoba del reparto de la masa regla 23: una persona sin dedicación cuya masa residual es inferior a este importe se imputa a (UJI, UJI) como gasto general; si es igual o superior, se mantiene en (pendiente, pendiente) como anomalía real a revisar.</t>
         </is>
       </c>
     </row>
